--- a/2025/FantasyPros NYJ-NE.xlsx
+++ b/2025/FantasyPros NYJ-NE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NFL-Fantasy\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB3DE2CF-23E0-431B-86F9-4EED705754E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6B5223-E850-4E1B-9DE5-525F8FBF5756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9CF84F4-DD42-40F8-BCAC-C4E4602F3F04}"/>
   </bookViews>
@@ -670,92 +670,103 @@
   <dimension ref="A1:AA46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="2.73046875" bestFit="1" customWidth="1"/>
     <col min="23" max="24" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.73046875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="1">
         <v>1</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="1">
         <v>2</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="1">
         <v>3</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="1">
         <v>4</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="1">
         <v>5</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="1">
         <v>6</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="1">
         <v>7</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="1">
         <v>8</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="1">
         <v>9</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="1">
         <v>10</v>
       </c>
-      <c r="O1">
+      <c r="O1" s="1">
         <v>11</v>
       </c>
-      <c r="P1">
+      <c r="P1" s="1">
         <v>12</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="1">
         <v>13</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="1">
         <v>14</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="1">
         <v>15</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="1">
         <v>16</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="1">
         <v>17</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="1">
         <v>18</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -808,6 +819,18 @@
       <c r="X2">
         <v>212.2</v>
       </c>
+      <c r="Y2">
+        <f t="shared" ref="Y2:Y20" si="0">MIN(E2:N2)</f>
+        <v>12.1</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" ref="Z2:Z20" si="1">MAX(E2:N2)</f>
+        <v>27.3</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" ref="AA2:AA20" si="2">MEDIAN(E2:N2)</f>
+        <v>21.65</v>
+      </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -858,6 +881,18 @@
       <c r="X3">
         <v>98.4</v>
       </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="1"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="2"/>
+        <v>9.65</v>
+      </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -905,6 +940,18 @@
       <c r="X4">
         <v>84.6</v>
       </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="1"/>
+        <v>23.8</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="2"/>
+        <v>8.1</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -955,6 +1002,18 @@
       <c r="X5">
         <v>82.9</v>
       </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="2"/>
+        <v>5.85</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -1005,6 +1064,18 @@
       <c r="X6">
         <v>79</v>
       </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -1055,6 +1126,18 @@
       <c r="X7">
         <v>76.7</v>
       </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="2"/>
+        <v>6.35</v>
+      </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -1105,6 +1188,18 @@
       <c r="X8">
         <v>73</v>
       </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -1149,6 +1244,18 @@
       <c r="X9">
         <v>66.8</v>
       </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>1.8</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="1"/>
+        <v>18.7</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -1199,6 +1306,18 @@
       <c r="X10">
         <v>58.3</v>
       </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="2"/>
+        <v>3.8000000000000003</v>
+      </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -1249,6 +1368,18 @@
       <c r="X11">
         <v>57.7</v>
       </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="1"/>
+        <v>13.6</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="2"/>
+        <v>5.5</v>
+      </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -1299,6 +1430,18 @@
       <c r="X12">
         <v>29.9</v>
       </c>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="1"/>
+        <v>8.1</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="2"/>
+        <v>2.7</v>
+      </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -1334,6 +1477,18 @@
       <c r="X13">
         <v>22.2</v>
       </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="1"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="2"/>
+        <v>3.1</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -1384,6 +1539,18 @@
       <c r="X14">
         <v>16.5</v>
       </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>-0.2</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="1"/>
+        <v>13.7</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -1416,6 +1583,18 @@
       <c r="X15">
         <v>14.7</v>
       </c>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>10.9</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="2"/>
+        <v>1.65</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -1442,6 +1621,18 @@
       <c r="X16">
         <v>0.1</v>
       </c>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A17">
@@ -1468,6 +1659,18 @@
       <c r="X17">
         <v>0.1</v>
       </c>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>-0.2</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="2"/>
+        <v>4.9999999999999989E-2</v>
+      </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A18">
@@ -1518,6 +1721,18 @@
       <c r="X18">
         <v>0</v>
       </c>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A19">
@@ -1550,6 +1765,18 @@
       <c r="X19">
         <v>0</v>
       </c>
+      <c r="Y19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A20">
@@ -1573,6 +1800,18 @@
       <c r="X20">
         <v>0</v>
       </c>
+      <c r="Y20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.45">
       <c r="D21" s="1" t="s">
@@ -1583,39 +1822,39 @@
         <v>85.2</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" ref="F21:N21" si="0">SUM(F2:F20)</f>
+        <f t="shared" ref="F21:N21" si="3">SUM(F2:F20)</f>
         <v>109.89999999999999</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>78.399999999999991</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>100.8</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>87.300000000000011</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>94.8</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>113.29999999999998</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>117.20000000000002</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>86.800000000000011</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>99.399999999999991</v>
       </c>
       <c r="O21" s="1"/>
@@ -1693,6 +1932,18 @@
       <c r="X23">
         <v>124.3</v>
       </c>
+      <c r="Y23">
+        <f t="shared" ref="Y23:Y45" si="4">MIN(E23:N23)</f>
+        <v>4</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" ref="Z23:Z45" si="5">MAX(E23:N23)</f>
+        <v>29.5</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" ref="AA23:AA45" si="6">MEDIAN(E23:N23)</f>
+        <v>14.45</v>
+      </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A24">
@@ -1743,6 +1994,18 @@
       <c r="X24">
         <v>119.6</v>
       </c>
+      <c r="Y24">
+        <f t="shared" si="4"/>
+        <v>4.8</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="5"/>
+        <v>31.9</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="6"/>
+        <v>13.6</v>
+      </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A25">
@@ -1793,6 +2056,18 @@
       <c r="X25">
         <v>84</v>
       </c>
+      <c r="Y25">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A26">
@@ -1837,6 +2112,18 @@
       <c r="X26">
         <v>81.5</v>
       </c>
+      <c r="Y26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="5"/>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="6"/>
+        <v>16.100000000000001</v>
+      </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A27">
@@ -1887,6 +2174,18 @@
       <c r="X27">
         <v>47.6</v>
       </c>
+      <c r="Y27">
+        <f t="shared" si="4"/>
+        <v>0.7</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="5"/>
+        <v>13.2</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="6"/>
+        <v>3.8</v>
+      </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A28">
@@ -1937,6 +2236,18 @@
       <c r="X28">
         <v>40</v>
       </c>
+      <c r="Y28">
+        <f t="shared" si="4"/>
+        <v>-3</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A29">
@@ -1987,6 +2298,18 @@
       <c r="X29">
         <v>33.200000000000003</v>
       </c>
+      <c r="Y29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="5"/>
+        <v>15.4</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="6"/>
+        <v>1.8</v>
+      </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A30">
@@ -2019,6 +2342,18 @@
       <c r="X30">
         <v>30.2</v>
       </c>
+      <c r="Y30">
+        <f t="shared" si="4"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="5"/>
+        <v>17.7</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="6"/>
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A31">
@@ -2066,6 +2401,18 @@
       <c r="X31">
         <v>29.7</v>
       </c>
+      <c r="Y31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="5"/>
+        <v>13.9</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="6"/>
+        <v>2.0499999999999998</v>
+      </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A32">
@@ -2116,6 +2463,18 @@
       <c r="X32">
         <v>20.6</v>
       </c>
+      <c r="Y32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="AA32">
+        <f t="shared" si="6"/>
+        <v>2.6</v>
+      </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A33">
@@ -2160,6 +2519,18 @@
       <c r="X33">
         <v>17.7</v>
       </c>
+      <c r="Y33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="5"/>
+        <v>9.1</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="6"/>
+        <v>1.25</v>
+      </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A34">
@@ -2198,6 +2569,18 @@
       <c r="X34">
         <v>17.600000000000001</v>
       </c>
+      <c r="Y34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="5"/>
+        <v>6.4</v>
+      </c>
+      <c r="AA34">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A35">
@@ -2233,6 +2616,18 @@
       <c r="X35">
         <v>14.3</v>
       </c>
+      <c r="Y35">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+      <c r="Z35">
+        <f t="shared" si="5"/>
+        <v>6.9</v>
+      </c>
+      <c r="AA35">
+        <f t="shared" si="6"/>
+        <v>3.4</v>
+      </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A36">
@@ -2274,6 +2669,18 @@
       <c r="X36">
         <v>14</v>
       </c>
+      <c r="Y36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="5"/>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AA36">
+        <f t="shared" si="6"/>
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A37">
@@ -2318,6 +2725,18 @@
       <c r="X37">
         <v>12</v>
       </c>
+      <c r="Y37">
+        <f t="shared" si="4"/>
+        <v>-2</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="5"/>
+        <v>7.1</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A38">
@@ -2368,6 +2787,18 @@
       <c r="X38">
         <v>9.1</v>
       </c>
+      <c r="Y38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="5"/>
+        <v>6.6</v>
+      </c>
+      <c r="AA38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A39">
@@ -2418,6 +2849,18 @@
       <c r="X39">
         <v>8</v>
       </c>
+      <c r="Y39">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="5"/>
+        <v>2.8</v>
+      </c>
+      <c r="AA39">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A40">
@@ -2453,6 +2896,18 @@
       <c r="X40">
         <v>6</v>
       </c>
+      <c r="Y40">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A41">
@@ -2500,6 +2955,18 @@
       <c r="X41">
         <v>3.9</v>
       </c>
+      <c r="Y41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AA41">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A42">
@@ -2532,6 +2999,18 @@
       <c r="X42">
         <v>0</v>
       </c>
+      <c r="Y42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A43">
@@ -2558,6 +3037,18 @@
       <c r="X43">
         <v>0</v>
       </c>
+      <c r="Y43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A44">
@@ -2587,6 +3078,18 @@
       <c r="X44">
         <v>0</v>
       </c>
+      <c r="Y44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A45">
@@ -2613,6 +3116,18 @@
       <c r="X45">
         <v>0</v>
       </c>
+      <c r="Y45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.45">
       <c r="D46" s="1" t="s">
@@ -2623,36 +3138,36 @@
         <v>100.79999999999998</v>
       </c>
       <c r="F46" s="1">
-        <f t="shared" ref="F46:N46" si="1">SUM(F23:F45)</f>
+        <f t="shared" ref="F46:N46" si="7">SUM(F23:F45)</f>
         <v>44.1</v>
       </c>
       <c r="G46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>87.8</v>
       </c>
       <c r="H46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>95.399999999999991</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>41</v>
       </c>
       <c r="K46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>52.399999999999991</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>118.20000000000002</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>72.3</v>
       </c>
       <c r="O46" s="1"/>
